--- a/report.xlsx
+++ b/report.xlsx
@@ -19,10 +19,10 @@
     <t>Files have differences.</t>
   </si>
   <si>
-    <t>[ChangeDelta, position: 0, lines: [This is the first sample text file.] to [This is the second sample text file.]]</t>
+    <t>[ChangeDelta, position: 2, lines: [Jane,25,London] to [Jane,28,London]]</t>
   </si>
   <si>
-    <t>[ChangeDelta, position: 2, lines: [The third line is unique to this file.] to [The third line is different in this file.]]</t>
+    <t>Mismatch at Table 1, Row 3, Col 2: '25' vs '28'</t>
   </si>
 </sst>
 </file>
@@ -82,17 +82,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
         <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -104,7 +99,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>